--- a/data/trans_dic/Predimed_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,4; 93,09</t>
+          <t>85,72; 93,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,99; 91,73</t>
+          <t>85,82; 91,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,85; 91,71</t>
+          <t>86,93; 91,87</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,26; 95,52</t>
+          <t>89,41; 95,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,54; 93,98</t>
+          <t>89,45; 94,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,17; 94,13</t>
+          <t>90,36; 94,2</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,0; 76,83</t>
+          <t>66,69; 77,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,73; 74,29</t>
+          <t>65,83; 74,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,04; 73,9</t>
+          <t>67,72; 74,05</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>54,59; 69,41</t>
+          <t>55,45; 70,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,45; 79,98</t>
+          <t>48,85; 78,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,8; 74,02</t>
+          <t>52,84; 73,74</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,19; 83,09</t>
+          <t>72,41; 82,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,3; 72,75</t>
+          <t>62,91; 72,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,03; 75,96</t>
+          <t>69,18; 76,01</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>81,05; 88,45</t>
+          <t>80,81; 88,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87,68; 93,08</t>
+          <t>88,04; 93,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,68; 89,85</t>
+          <t>85,17; 90,15</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64,5; 73,45</t>
+          <t>64,95; 73,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,24; 91,0</t>
+          <t>69,07; 89,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,84; 82,78</t>
+          <t>68,68; 84,05</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>95,68; 98,98</t>
+          <t>95,63; 98,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90,98; 95,4</t>
+          <t>91,03; 95,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,33; 97,56</t>
+          <t>94,31; 97,43</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>82,11; 87,88</t>
+          <t>82,05; 87,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78,97; 85,12</t>
+          <t>79,16; 85,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81,06; 85,18</t>
+          <t>81,18; 85,25</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con una adherencia baja a la dieta mediterránea</t>
+          <t>Población con una adherencia baja a la dieta mediterránea (tasa de respuesta: 94,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>267760; 288481</t>
+          <t>265647; 288412</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>248624; 265233</t>
+          <t>248134; 265602</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>520300; 549407</t>
+          <t>520781; 550318</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>392918; 420448</t>
+          <t>393556; 420881</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>411662; 432081</t>
+          <t>411230; 432133</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>811443; 847093</t>
+          <t>813167; 847731</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>196623; 225455</t>
+          <t>195703; 226439</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>212916; 240628</t>
+          <t>213233; 239872</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>413858; 456246</t>
+          <t>418092; 457152</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>132465; 168429</t>
+          <t>134542; 170396</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>194800; 321557</t>
+          <t>196393; 315275</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>340416; 477223</t>
+          <t>340686; 475382</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>125309; 144221</t>
+          <t>125684; 143906</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>128859; 148107</t>
+          <t>128069; 147766</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>260366; 286484</t>
+          <t>260933; 286686</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>216438; 236209</t>
+          <t>215808; 236963</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>223238; 237005</t>
+          <t>224155; 237513</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>441727; 468697</t>
+          <t>444278; 470260</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>377500; 429916</t>
+          <t>380135; 428458</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>569291; 748202</t>
+          <t>567867; 738418</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>968950; 1165120</t>
+          <t>966611; 1183051</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>874695; 904909</t>
+          <t>874301; 904637</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>642755; 674039</t>
+          <t>643144; 673443</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1528768; 1581125</t>
+          <t>1528599; 1579145</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2649186; 2835376</t>
+          <t>2647321; 2829739</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2733822; 2946526</t>
+          <t>2740215; 2946594</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5421362; 5697167</t>
+          <t>5429194; 5701654</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Predimed_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Predimed_R2-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,72; 93,06</t>
+          <t>85,89; 92,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,82; 91,86</t>
+          <t>86,98; 92,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,93; 91,87</t>
+          <t>87,52; 91,75</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,41; 95,61</t>
+          <t>89,63; 95,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,45; 94,0</t>
+          <t>89,73; 94,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,36; 94,2</t>
+          <t>90,88; 94,39</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>66,69; 77,16</t>
+          <t>67,06; 76,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,83; 74,06</t>
+          <t>65,95; 74,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,72; 74,05</t>
+          <t>67,54; 74,16</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>59,96%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,45; 70,22</t>
+          <t>51,81; 66,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,85; 78,42</t>
+          <t>55,31; 65,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,84; 73,74</t>
+          <t>55,61; 64,07</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,41; 82,9</t>
+          <t>73,91; 84,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,91; 72,59</t>
+          <t>63,54; 73,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,18; 76,01</t>
+          <t>70,49; 77,11</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>80,81; 88,74</t>
+          <t>80,91; 88,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88,04; 93,28</t>
+          <t>87,15; 92,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,17; 90,15</t>
+          <t>85,34; 89,93</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>69,35%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>64,95; 73,2</t>
+          <t>64,98; 72,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,07; 89,81</t>
+          <t>65,98; 72,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,68; 84,05</t>
+          <t>66,46; 71,78</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>95,63; 98,95</t>
+          <t>94,79; 97,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,03; 95,32</t>
+          <t>92,96; 95,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,31; 97,43</t>
+          <t>94,33; 96,46</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>82,05; 87,71</t>
+          <t>80,74; 83,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79,16; 85,12</t>
+          <t>79,84; 82,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81,18; 85,25</t>
+          <t>80,7; 82,69</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>279309</t>
+          <t>284277</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>257828</t>
+          <t>283910</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>537137</t>
+          <t>568187</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>265647; 288412</t>
+          <t>272791; 293677</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>248134; 265602</t>
+          <t>274506; 291094</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>520781; 550318</t>
+          <t>554176; 580936</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>410159</t>
+          <t>424163</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>422575</t>
+          <t>451044</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>832734</t>
+          <t>875206</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>393556; 420881</t>
+          <t>407532; 433574</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>411230; 432133</t>
+          <t>438543; 459873</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>813167; 847731</t>
+          <t>857374; 890550</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>210804</t>
+          <t>212428</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>226596</t>
+          <t>231827</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437400</t>
+          <t>444255</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>195703; 226439</t>
+          <t>197210; 225533</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>213233; 239872</t>
+          <t>217755; 244943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>418092; 457152</t>
+          <t>421616; 462930</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>152163</t>
+          <t>170446</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>249406</t>
+          <t>203350</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>401569</t>
+          <t>373795</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>134542; 170396</t>
+          <t>148464; 190633</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>196393; 315275</t>
+          <t>186329; 220744</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>340686; 475382</t>
+          <t>346712; 399419</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>135604</t>
+          <t>159450</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>138881</t>
+          <t>153215</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274486</t>
+          <t>312664</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>125684; 143906</t>
+          <t>147997; 168277</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>128069; 147766</t>
+          <t>141752; 163529</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>260933; 286686</t>
+          <t>298414; 326419</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>227018</t>
+          <t>228299</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>230872</t>
+          <t>236266</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>457891</t>
+          <t>464565</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>215808; 236963</t>
+          <t>216987; 237679</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>224155; 237513</t>
+          <t>227682; 242369</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>444278; 470260</t>
+          <t>451830; 476143</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>404666</t>
+          <t>465340</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>637652</t>
+          <t>513142</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1042319</t>
+          <t>978481</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>380135; 428458</t>
+          <t>437839; 491174</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>567867; 738418</t>
+          <t>486298; 534572</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>966611; 1183051</t>
+          <t>937700; 1012736</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>890119</t>
+          <t>755414</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>662599</t>
+          <t>774615</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1552718</t>
+          <t>1530028</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>874301; 904637</t>
+          <t>741362; 764166</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>643144; 673443</t>
+          <t>761174; 785784</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1528599; 1579145</t>
+          <t>1510169; 1544249</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2709843</t>
+          <t>2699816</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2826408</t>
+          <t>2847367</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5536252</t>
+          <t>5547183</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2647321; 2829739</t>
+          <t>2645926; 2743604</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2740215; 2946594</t>
+          <t>2803606; 2885880</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5429194; 5701654</t>
+          <t>5478334; 5613500</t>
         </is>
       </c>
     </row>
